--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="38.5"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="35.2"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="19.8"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="5.5"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 8</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
@@ -78,7 +78,7 @@
     <col min="6" max="6" bestFit="1" customWidth="1" width="38.5"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="35.2"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="19.8"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" width="11.0"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" width="12.100000000000001"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -175,16 +175,16 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>09:00 EDT</t>
+          <t>12:00 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -194,17 +194,17 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 8</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>Manhattan Kickers MKSC 2014/2015</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Bushwick Inlet Park - Field 1 9v9</t>
+          <t>Pier 42 - Pier 42 11v11</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Sunday, October 18, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>12:00 EDT</t>
+          <t>10:00 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
+          <t>French Football Academy 2014/15 Digne</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>1 - 8</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Manhattan Kickers MKSC 2014/2015</t>
+          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Pier 42 - Pier 42 11v11</t>
+          <t>Randall's Island - 70</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -259,27 +259,27 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 18, 2026</t>
+          <t>Saturday, October 24, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>09:10 EDT</t>
+          <t>09:15 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>French Football Academy 2014/15 Digne</t>
+          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -289,12 +289,12 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
+          <t>Excelsior New York Academy 2014/2015 Boys</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>Randall's Island - 82</t>
+          <t>Frank Principe Park/ Maurice Park Soccer 04  - Field 4</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -310,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Saturday, October 31, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>09:15 EDT</t>
+          <t>08:00 EDT</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>Excelsior New York Academy 2014/2015 Boys</t>
+          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Frank Principe Park/ Maurice Park Soccer 04  - Field 4</t>
+          <t>Dyker Turf Field B Small Sided  - B</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -355,21 +355,21 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Saturday, November  7, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>08:00 EDT</t>
+          <t>19:00 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Strand Larsen</t>
+          <t>Manhattan Kickers MKSC 2014/2015</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -384,7 +384,7 @@
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field B Small Sided  - B</t>
+          <t>Con Edison Field- Manhattan - 1- Manhattan</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -400,21 +400,21 @@
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November  7, 2026</t>
+          <t>Saturday, November 21, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>19:00 EST</t>
+          <t>08:45 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>Manhattan Kickers MKSC 2014/2015</t>
+          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>ALBION SC Brooklyn B14/15 Premier - Williamsburg</t>
+          <t>French Football Academy 2014/15 Digne</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Con Edison Field- Manhattan - 1- Manhattan</t>
+          <t>Frank Principe Park  - East Field </t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -445,7 +445,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
@@ -454,7 +454,7 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>08:45 EST</t>
+          <t>14:00 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>French Football Academy 2014/15 Digne</t>
+          <t>SC Gjoa Strand Larsen</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Frank Principe Park  - East Field </t>
+          <t>Bush Terminal Piers Park - Soccer 03 (Back field)</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7 - 2</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b14-15-premier-williamsburg.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 - 4</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
